--- a/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -296,7 +296,7 @@
     <t>fr-lm-traitement.medicament</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-produit-sante
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.35546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.54296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -286,7 +286,7 @@
     <t>fr-lm-traitement.dosage</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-posologie
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dosage-instructions
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.54296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.25" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-traitement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
